--- a/results/job_matches_2026-09-08.xlsx
+++ b/results/job_matches_2026-09-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NBME</t>
+          <t>Visibol</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Sqoop, HBase, Scala, Snowflake, Oracle</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f3d0c20a7e71fe</t>
+          <t>https://www.indeed.com/viewjob?jk=0d15bd8d2dcde66c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Visibol</t>
+          <t>arrivia</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d15bd8d2dcde66c</t>
+          <t>https://www.indeed.com/viewjob?jk=1050647a13a073f5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Cloud Solutions Architect 2 (Contractor) - 529701772</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>arrivia</t>
+          <t>RE/SPEC Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1050647a13a073f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c458c043196a1c69</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 2 (Contractor) - 529701772</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RE/SPEC Inc</t>
+          <t>Stream</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c458c043196a1c69</t>
+          <t>https://www.indeed.com/viewjob?jk=3bddb4afe7c4caf5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stream</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bddb4afe7c4caf5</t>
+          <t>https://www.indeed.com/viewjob?jk=65dc6fa390e72ae6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-Stack Engineer - Albany</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Rocket Science Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
+          <t>Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65dc6fa390e72ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=a173f8b22852bf0b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer - Albany</t>
+          <t>Data Engineer - Databricks &amp; dbt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rocket Science Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a173f8b22852bf0b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d233d87b66cf8ac</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks &amp; dbt</t>
+          <t>Data Engineer / Architect – Databricks &amp; dbt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d233d87b66cf8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=8d01e7837ac03015</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer / Architect – Databricks &amp; dbt</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Semicon Service Nordic AB</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, dbt</t>
+          <t>AWS, Azure, GCP, BigQuery, Kafka, Oracle, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,112 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d01e7837ac03015</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Semicon Service Nordic AB</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, BigQuery, Kafka, Oracle, CI/CD, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=b82b7e5b56d16b4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Racine, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=001eb9aca1486771</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Cloud Network Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ardor Digital Inc</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a26a714c52ecd818</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-08.xlsx
+++ b/results/job_matches_2026-09-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer - Albany</t>
+          <t>Data Engineer - Databricks &amp; dbt</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rocket Science Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a173f8b22852bf0b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d233d87b66cf8ac</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks &amp; dbt</t>
+          <t>Data Engineer / Architect – Databricks &amp; dbt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d233d87b66cf8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=8d01e7837ac03015</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer / Architect – Databricks &amp; dbt</t>
+          <t>Software Developer / Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JOb Assist</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,56 +727,21 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d01e7837ac03015</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Semicon Service Nordic AB</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, BigQuery, Kafka, Oracle, CI/CD, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b82b7e5b56d16b4c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4b70d4e466c6eb</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-08.xlsx
+++ b/results/job_matches_2026-09-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Visibol</t>
+          <t>arrivia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d15bd8d2dcde66c</t>
+          <t>https://www.indeed.com/viewjob?jk=1050647a13a073f5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>arrivia</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1050647a13a073f5</t>
+          <t>https://www.indeed.com/viewjob?jk=50af554e5fcbec22</t>
         </is>
       </c>
     </row>
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Quality Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stream</t>
+          <t>Protolabs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Maple Plain, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,52 +591,52 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, dbt, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bddb4afe7c4caf5</t>
+          <t>https://www.indeed.com/viewjob?jk=50167c9262a6f352</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Catalina Business Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
+          <t>AWS, S3, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65dc6fa390e72ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=583047aa0c29e841</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Developer / Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JOb Assist</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,15 +731,50 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Azure, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Azure DevOps, Kubernetes, pytest, Git</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d342c243987526b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Software Developer / Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JOb Assist</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5e4b70d4e466c6eb</t>
         </is>

--- a/results/job_matches_2026-09-08.xlsx
+++ b/results/job_matches_2026-09-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Sr. Azure Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>arrivia</t>
+          <t>FSS Government Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1050647a13a073f5</t>
+          <t>https://www.indeed.com/viewjob?jk=2c906b9319ac1927</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,15 +513,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af554e5fcbec22</t>
+          <t>https://www.indeed.com/viewjob?jk=deb3c79369e1483f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect 2 (Contractor) - 529701772</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RE/SPEC Inc</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c458c043196a1c69</t>
+          <t>https://www.indeed.com/viewjob?jk=40929f510d8aea9b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Quality Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Protolabs</t>
+          <t>arrivia</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Maple Plain, MN, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, dbt, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50167c9262a6f352</t>
+          <t>https://www.indeed.com/viewjob?jk=1050647a13a073f5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Snowflake Solutions Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Catalina Business Solutions</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583047aa0c29e841</t>
+          <t>https://www.indeed.com/viewjob?jk=04573f87a8122729</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks &amp; dbt</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d233d87b66cf8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=50af554e5fcbec22</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer / Architect – Databricks &amp; dbt</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, dbt</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d01e7837ac03015</t>
+          <t>https://www.indeed.com/viewjob?jk=8708b9448e952fad</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Operations Data Engineer (On Site Only)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Zoll Medical Corporation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Azure DevOps, Kubernetes, pytest, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,1967 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d342c243987526b3</t>
+          <t>https://www.indeed.com/viewjob?jk=606ded7f86fcb046</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Infrastructure Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ThinkMirum, Inc.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Henrico, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7540868c3f94cca8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Terrabis</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Dimension Tables, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96ab0aae8b810da1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Engineer II, Analytics &amp; Modeling</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CLEAR</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf7c4f2948adca69</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Engineer III - Platform Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b4b81b7d3a7707c</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Long Key, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=860b23040114a8d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Jackson, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7318de585b9240c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39a63e8d41e47b1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Montpelier, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bfdc237a5ec2521a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96dbbd28de91d8d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f7a086e893f74d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Pierre, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92b76ff97226a6fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Middletown, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c823f162806160da</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42745e2b7d3b4f70</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86dbb6e245ef6f03</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=803cad2315014c66</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Pawtucket, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21001c0e4015b94c</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=067ba8dc4ea90456</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hope Hull, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca747d14a8213963</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=100a2578e0de9a9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b27b5a5a2dbd7b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7650cf6efa152d46</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fdab35fb5d301b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8d9249e36a5a6f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Hot Springs Village, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9dfa47cceff7481b</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Corrales, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b32034eb11b34213</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Charleston, WV, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9451dd40e73a7e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c80a95d3d6ee6292</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de47c019dcb8f48a</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Kennesaw, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3900a08ed626684f</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Augusta, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=592a07a140bc3c31</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Fremont, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d85fc6a7df757e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=012126d96bacab86</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Okemos, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25faed0ee0f87e0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4f528d7c6591cc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd1b53baaf5bb73e</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4e0147cefbb8eb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Kansas City, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be56d1f6c8fed56c</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=724cac9c095efeeb</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>New Franken, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ad205890083815e</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6ee3ad0f2f5a12f</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e639c4f4fc356279</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0bc7bce3b199252</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d02ce8ad5ba0ffc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7e42009318b0530</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5620acaf132d6433</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85ded7658087672f</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Walnut Creek, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c301099fdc12e291</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Columbia, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96c1789a53f8e267</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Upper Darby, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=803b2cfe22724310</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=805ba729e77c2f20</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a7ddd4398f2504b</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>AWS Database Architect</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Tachyon Technologies</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, IAM, RDS, Kafka, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7089341fcf260484</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Business Analyst (SQL &amp; Snowflake)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unitedone health</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, Talend, dbt</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bcad9584a9c6b560</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>FDM Group</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Azure DevOps, Kubernetes, pytest, Git</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d342c243987526b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>Software Developer / Engineer</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>JOb Assist</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D64" t="n">
         <v>10.4</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5e4b70d4e466c6eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Software &amp; System Design Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>American Honda Motor</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Torrance, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, SQL Server, Terraform, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d4cff3d4e2e95ec</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-08.xlsx
+++ b/results/job_matches_2026-09-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Azure Architect</t>
+          <t>Engineer II, Data (Cloud &amp; AI)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FSS Government Solutions</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Blob Storage, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c906b9319ac1927</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c022ecfcaf20c6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Sr. Azure Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FSS Government Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb3c79369e1483f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c906b9319ac1927</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40929f510d8aea9b</t>
+          <t>https://www.indeed.com/viewjob?jk=deb3c79369e1483f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>arrivia</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1050647a13a073f5</t>
+          <t>https://www.indeed.com/viewjob?jk=40929f510d8aea9b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Snowflake Solutions Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>LOJELIS US</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04573f87a8122729</t>
+          <t>https://www.indeed.com/viewjob?jk=389f31eefdd51556</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>arrivia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af554e5fcbec22</t>
+          <t>https://www.indeed.com/viewjob?jk=1050647a13a073f5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Solutions Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8708b9448e952fad</t>
+          <t>https://www.indeed.com/viewjob?jk=04573f87a8122729</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Operations Data Engineer (On Site Only)</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Zoll Medical Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606ded7f86fcb046</t>
+          <t>https://www.indeed.com/viewjob?jk=50af554e5fcbec22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ThinkMirum, Inc.</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Henrico, VA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7540868c3f94cca8</t>
+          <t>https://www.indeed.com/viewjob?jk=8708b9448e952fad</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Operations Data Engineer (On Site Only)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Terrabis</t>
+          <t>Zoll Medical Corporation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Dimension Tables, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ab0aae8b810da1</t>
+          <t>https://www.indeed.com/viewjob?jk=606ded7f86fcb046</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II, Analytics &amp; Modeling</t>
+          <t>Infrastructure Solutions Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>ThinkMirum, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Henrico, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf7c4f2948adca69</t>
+          <t>https://www.indeed.com/viewjob?jk=7540868c3f94cca8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Engineer III - Platform Data Engineer (Remote)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Terrabis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Dimension Tables, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4b81b7d3a7707c</t>
+          <t>https://www.indeed.com/viewjob?jk=96ab0aae8b810da1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860b23040114a8d8</t>
+          <t>https://www.indeed.com/viewjob?jk=b33ee0863e9fcfb3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Data Engineer II, Analytics &amp; Modeling</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7318de585b9240c9</t>
+          <t>https://www.indeed.com/viewjob?jk=bf7c4f2948adca69</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Engineer III - Platform Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a63e8d41e47b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4b81b7d3a7707c</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfdc237a5ec2521a</t>
+          <t>https://www.indeed.com/viewjob?jk=7318de585b9240c9</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96dbbd28de91d8d7</t>
+          <t>https://www.indeed.com/viewjob?jk=39a63e8d41e47b1d</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f7a086e893f74d3</t>
+          <t>https://www.indeed.com/viewjob?jk=bfdc237a5ec2521a</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b76ff97226a6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=860b23040114a8d8</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c823f162806160da</t>
+          <t>https://www.indeed.com/viewjob?jk=96dbbd28de91d8d7</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42745e2b7d3b4f70</t>
+          <t>https://www.indeed.com/viewjob?jk=0f7a086e893f74d3</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86dbb6e245ef6f03</t>
+          <t>https://www.indeed.com/viewjob?jk=92b76ff97226a6fc</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803cad2315014c66</t>
+          <t>https://www.indeed.com/viewjob?jk=c823f162806160da</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21001c0e4015b94c</t>
+          <t>https://www.indeed.com/viewjob?jk=42745e2b7d3b4f70</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067ba8dc4ea90456</t>
+          <t>https://www.indeed.com/viewjob?jk=86dbb6e245ef6f03</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca747d14a8213963</t>
+          <t>https://www.indeed.com/viewjob?jk=803cad2315014c66</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100a2578e0de9a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=21001c0e4015b94c</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b27b5a5a2dbd7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=067ba8dc4ea90456</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7650cf6efa152d46</t>
+          <t>https://www.indeed.com/viewjob?jk=ca747d14a8213963</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fdab35fb5d301b8</t>
+          <t>https://www.indeed.com/viewjob?jk=100a2578e0de9a9a</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8d9249e36a5a6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=0b27b5a5a2dbd7b8</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dfa47cceff7481b</t>
+          <t>https://www.indeed.com/viewjob?jk=7650cf6efa152d46</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32034eb11b34213</t>
+          <t>https://www.indeed.com/viewjob?jk=5fdab35fb5d301b8</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9451dd40e73a7e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b8d9249e36a5a6f6</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a95d3d6ee6292</t>
+          <t>https://www.indeed.com/viewjob?jk=9dfa47cceff7481b</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de47c019dcb8f48a</t>
+          <t>https://www.indeed.com/viewjob?jk=b32034eb11b34213</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3900a08ed626684f</t>
+          <t>https://www.indeed.com/viewjob?jk=c9451dd40e73a7e8</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592a07a140bc3c31</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a95d3d6ee6292</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d85fc6a7df757e7</t>
+          <t>https://www.indeed.com/viewjob?jk=de47c019dcb8f48a</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=012126d96bacab86</t>
+          <t>https://www.indeed.com/viewjob?jk=3900a08ed626684f</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Okemos, MI, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25faed0ee0f87e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=592a07a140bc3c31</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f528d7c6591cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=4d85fc6a7df757e7</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1b53baaf5bb73e</t>
+          <t>https://www.indeed.com/viewjob?jk=012126d96bacab86</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e0147cefbb8eb1</t>
+          <t>https://www.indeed.com/viewjob?jk=25faed0ee0f87e0b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be56d1f6c8fed56c</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f528d7c6591cc6</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724cac9c095efeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1b53baaf5bb73e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New Franken, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad205890083815e</t>
+          <t>https://www.indeed.com/viewjob?jk=e4e0147cefbb8eb1</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6ee3ad0f2f5a12f</t>
+          <t>https://www.indeed.com/viewjob?jk=be56d1f6c8fed56c</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e639c4f4fc356279</t>
+          <t>https://www.indeed.com/viewjob?jk=724cac9c095efeeb</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bc7bce3b199252</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad205890083815e</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02ce8ad5ba0ffc3</t>
+          <t>https://www.indeed.com/viewjob?jk=a6ee3ad0f2f5a12f</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e42009318b0530</t>
+          <t>https://www.indeed.com/viewjob?jk=e639c4f4fc356279</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5620acaf132d6433</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bc7bce3b199252</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85ded7658087672f</t>
+          <t>https://www.indeed.com/viewjob?jk=d02ce8ad5ba0ffc3</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c301099fdc12e291</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e42009318b0530</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c1789a53f8e267</t>
+          <t>https://www.indeed.com/viewjob?jk=5620acaf132d6433</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Upper Darby, PA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803b2cfe22724310</t>
+          <t>https://www.indeed.com/viewjob?jk=85ded7658087672f</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805ba729e77c2f20</t>
+          <t>https://www.indeed.com/viewjob?jk=c301099fdc12e291</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7ddd4398f2504b</t>
+          <t>https://www.indeed.com/viewjob?jk=96c1789a53f8e267</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AWS Database Architect</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tachyon Technologies</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Upper Darby, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, IAM, RDS, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7089341fcf260484</t>
+          <t>https://www.indeed.com/viewjob?jk=803b2cfe22724310</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Business Analyst (SQL &amp; Snowflake)</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Unitedone health</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, Talend, dbt</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcad9584a9c6b560</t>
+          <t>https://www.indeed.com/viewjob?jk=805ba729e77c2f20</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior .Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Azure DevOps, Kubernetes, pytest, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d342c243987526b3</t>
+          <t>https://www.indeed.com/viewjob?jk=24127d299155c458</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Developer / Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JOb Assist</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,40 +2666,600 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4b70d4e466c6eb</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7ddd4398f2504b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>Data Product Engineer (Databricks)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64db87397886bc2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>AWS Database Architect</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Tachyon Technologies</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, IAM, RDS, Kafka, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7089341fcf260484</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Business Analyst (SQL &amp; Snowflake)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unitedone health</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, Talend, dbt</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bcad9584a9c6b560</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Data Engineer I</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Snowflake Schema, ETL, dbt</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=547acd1166eac18c</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Speech &amp; LLM Training Data</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Propio LS LLC</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Step Functions, S3, IAM, Databricks, Spark, PySpark, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=807824f66dc0a84a</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Microsoft Fabric Data Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Landmark Properties, Inc.</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Athens, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e98e4f56ed833c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Microsoft Fabric Data Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Landmark Properties, Inc.</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8eec69955d73cd72</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Katalyst Data Management</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a5ab3490cf1d4af</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Full Stack</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fbaf369c2bba2b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Full Stack UI Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Quantum US</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Centennial, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f21984098565a1d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Azure Databricks Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, ELT, MLflow, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5e6f301d4219633</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sr. Quality Assurance Analyst</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Broadcast Music</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f947c468dcbd787</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Python Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ATG</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>North Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd497236bc21a443</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Data modeler- ETL</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4a609b29094569b</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>FDM Group</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Azure DevOps, Kubernetes, pytest, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d342c243987526b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Software Developer / Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>JOb Assist</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e4b70d4e466c6eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>Software &amp; System Design Engineer</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>American Honda Motor</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Torrance, CA, US USA</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D81" t="n">
         <v>10.4</v>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>AWS, S3, IAM, RDS, Scala, Oracle, SQL Server, Terraform, Git, CloudWatch</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4d4cff3d4e2e95ec</t>
         </is>
